--- a/02-Cavidade não conforme/Colas/Arruela/01-22-11-23-Arruela de vedação para cola - 2 cav. - Molde 202.xlsx
+++ b/02-Cavidade não conforme/Colas/Arruela/01-22-11-23-Arruela de vedação para cola - 2 cav. - Molde 202.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\09-Inspeção Setores\02-Injetoras\01-Cavidades não conforme\02-Cavidade não conforme\Colas\Arruela\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avila\Downloads\Nova pasta (2)\02-Cavidade não conforme\Colas\Arruela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51709863-B7E3-4532-A4AC-31C895E0BC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F53A49E-A9F0-45D9-A14A-5A3EB4AB4323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,11 +19,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Plan1!$A$1:$P$58</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>CAVIDADES NÃO CONFORMES</t>
   </si>
@@ -218,9 +223,6 @@
     <t>ROMI 39</t>
   </si>
   <si>
-    <t>MARLON</t>
-  </si>
-  <si>
     <t>TPE</t>
   </si>
 </sst>
@@ -919,44 +921,122 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -964,17 +1044,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -982,47 +1062,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1034,15 +1078,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1102,100 +1137,67 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1836,46 +1838,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96"/>
-      <c r="B1" s="97"/>
-      <c r="C1" s="100" t="s">
+      <c r="A1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="105" t="s">
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="107"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="51"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="98"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="108" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="110"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="54"/>
     </row>
     <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1887,39 +1889,39 @@
       <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="111" t="s">
+      <c r="D3" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="112"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="H3" s="20" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="23"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
       <c r="P3" s="24"/>
     </row>
     <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="54">
+      <c r="A4" s="60">
         <v>1</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="40" t="s">
+      <c r="B4" s="62"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="48" t="s">
+      <c r="E4" s="68"/>
+      <c r="F4" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="46"/>
-      <c r="H4" s="51"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="57"/>
       <c r="I4" s="25"/>
       <c r="J4" s="6"/>
       <c r="K4" s="21"/>
@@ -1930,14 +1932,14 @@
       <c r="P4" s="7"/>
     </row>
     <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="55"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="52"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="25"/>
       <c r="J5" s="6"/>
       <c r="K5" s="21"/>
@@ -1948,14 +1950,14 @@
       <c r="P5" s="7"/>
     </row>
     <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="60"/>
-      <c r="B6" s="61"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="53"/>
+      <c r="A6" s="75"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="59"/>
       <c r="I6" s="25"/>
       <c r="J6" s="6"/>
       <c r="K6" s="21"/>
@@ -1966,20 +1968,20 @@
       <c r="P6" s="7"/>
     </row>
     <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="54">
+      <c r="A7" s="60">
         <v>2</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="40" t="s">
+      <c r="B7" s="62"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="43"/>
-      <c r="F7" s="48" t="s">
+      <c r="E7" s="68"/>
+      <c r="F7" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="46"/>
-      <c r="H7" s="51"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="57"/>
       <c r="I7" s="25"/>
       <c r="J7" s="6"/>
       <c r="K7" s="21"/>
@@ -1990,14 +1992,14 @@
       <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="55"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="52"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="58"/>
       <c r="I8" s="25"/>
       <c r="J8" s="6"/>
       <c r="K8" s="21"/>
@@ -2008,14 +2010,14 @@
       <c r="P8" s="7"/>
     </row>
     <row r="9" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="52"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="58"/>
       <c r="I9" s="25"/>
       <c r="J9" s="6"/>
       <c r="K9" s="21"/>
@@ -2026,14 +2028,14 @@
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="39"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="34"/>
+      <c r="A10" s="110"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="102"/>
       <c r="I10" s="25"/>
       <c r="J10" s="6"/>
       <c r="K10" s="21"/>
@@ -2044,14 +2046,14 @@
       <c r="P10" s="7"/>
     </row>
     <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="117"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="27"/>
+      <c r="A11" s="104"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="103"/>
       <c r="I11" s="25"/>
       <c r="J11" s="6"/>
       <c r="K11" s="21"/>
@@ -2062,14 +2064,14 @@
       <c r="P11" s="7"/>
     </row>
     <row r="12" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="113"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="116"/>
-      <c r="H12" s="27"/>
+      <c r="A12" s="104"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="109"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="103"/>
       <c r="I12" s="25"/>
       <c r="J12" s="6"/>
       <c r="K12" s="21"/>
@@ -2080,14 +2082,14 @@
       <c r="P12" s="7"/>
     </row>
     <row r="13" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="113"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="116"/>
-      <c r="H13" s="27"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="103"/>
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -2098,14 +2100,14 @@
       <c r="P13" s="7"/>
     </row>
     <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="113"/>
-      <c r="C14" s="119"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="116"/>
-      <c r="H14" s="27"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="103"/>
       <c r="I14" s="5"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
@@ -2116,14 +2118,14 @@
       <c r="P14" s="7"/>
     </row>
     <row r="15" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="113"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="116"/>
-      <c r="H15" s="27"/>
+      <c r="A15" s="104"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="103"/>
       <c r="I15" s="5"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
@@ -2134,14 +2136,14 @@
       <c r="P15" s="7"/>
     </row>
     <row r="16" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="113"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="116"/>
-      <c r="H16" s="27"/>
+      <c r="A16" s="104"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="103"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
@@ -2150,21 +2152,21 @@
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="7"/>
-      <c r="U16" s="88"/>
-      <c r="V16" s="88"/>
-      <c r="W16" s="88"/>
-      <c r="X16" s="88"/>
-      <c r="Y16" s="88"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
     </row>
     <row r="17" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="27"/>
+      <c r="A17" s="104"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="103"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
@@ -2173,21 +2175,21 @@
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="7"/>
-      <c r="U17" s="89"/>
-      <c r="V17" s="89"/>
-      <c r="W17" s="89"/>
-      <c r="X17" s="89"/>
-      <c r="Y17" s="89"/>
+      <c r="U17" s="28"/>
+      <c r="V17" s="28"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="28"/>
+      <c r="Y17" s="28"/>
     </row>
     <row r="18" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="27"/>
+      <c r="A18" s="104"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="103"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
@@ -2198,14 +2200,14 @@
       <c r="P18" s="7"/>
     </row>
     <row r="19" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="27"/>
+      <c r="A19" s="104"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="103"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
@@ -2216,14 +2218,14 @@
       <c r="P19" s="7"/>
     </row>
     <row r="20" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="27"/>
+      <c r="A20" s="104"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="103"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -2234,14 +2236,14 @@
       <c r="P20" s="7"/>
     </row>
     <row r="21" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="27"/>
+      <c r="A21" s="104"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="103"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
@@ -2252,14 +2254,14 @@
       <c r="P21" s="7"/>
     </row>
     <row r="22" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="27"/>
+      <c r="A22" s="104"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="103"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
@@ -2270,14 +2272,14 @@
       <c r="P22" s="7"/>
     </row>
     <row r="23" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="27"/>
+      <c r="A23" s="104"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="103"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
@@ -2288,14 +2290,14 @@
       <c r="P23" s="7"/>
     </row>
     <row r="24" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="27"/>
+      <c r="A24" s="104"/>
+      <c r="B24" s="115"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="103"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
@@ -2306,14 +2308,14 @@
       <c r="P24" s="7"/>
     </row>
     <row r="25" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="27"/>
+      <c r="A25" s="104"/>
+      <c r="B25" s="115"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="103"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
@@ -2324,14 +2326,14 @@
       <c r="P25" s="7"/>
     </row>
     <row r="26" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="27"/>
+      <c r="A26" s="104"/>
+      <c r="B26" s="115"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="103"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
@@ -2342,14 +2344,14 @@
       <c r="P26" s="7"/>
     </row>
     <row r="27" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="27"/>
+      <c r="A27" s="104"/>
+      <c r="B27" s="115"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="118"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="103"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
@@ -2360,14 +2362,14 @@
       <c r="P27" s="7"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="27"/>
+      <c r="A28" s="104"/>
+      <c r="B28" s="115"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="103"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
@@ -2378,14 +2380,14 @@
       <c r="P28" s="7"/>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="27"/>
+      <c r="A29" s="104"/>
+      <c r="B29" s="115"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="103"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
@@ -2396,14 +2398,14 @@
       <c r="P29" s="7"/>
     </row>
     <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="27"/>
+      <c r="A30" s="104"/>
+      <c r="B30" s="115"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="103"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
@@ -2414,14 +2416,14 @@
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="27"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="115"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="118"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="103"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
@@ -2432,14 +2434,14 @@
       <c r="P31" s="7"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="27"/>
+      <c r="A32" s="104"/>
+      <c r="B32" s="115"/>
+      <c r="C32" s="116"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="103"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
@@ -2450,14 +2452,14 @@
       <c r="P32" s="7"/>
     </row>
     <row r="33" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="27"/>
+      <c r="A33" s="104"/>
+      <c r="B33" s="115"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="118"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="103"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -2468,358 +2470,356 @@
       <c r="P33" s="7"/>
     </row>
     <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="92"/>
+      <c r="A34" s="104"/>
+      <c r="B34" s="115"/>
+      <c r="C34" s="116"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="118"/>
+      <c r="G34" s="117"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
+      <c r="P34" s="35"/>
     </row>
     <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="93"/>
+      <c r="A35" s="104"/>
+      <c r="B35" s="115"/>
+      <c r="C35" s="116"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="117"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="117"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="36"/>
+      <c r="M35" s="36"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="36"/>
+      <c r="P35" s="37"/>
     </row>
     <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="93"/>
+      <c r="A36" s="104"/>
+      <c r="B36" s="115"/>
+      <c r="C36" s="116"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="118"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="37"/>
     </row>
     <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="93"/>
+      <c r="A37" s="104"/>
+      <c r="B37" s="115"/>
+      <c r="C37" s="116"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="37"/>
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-      <c r="N38" s="31"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="93"/>
+      <c r="A38" s="104"/>
+      <c r="B38" s="115"/>
+      <c r="C38" s="116"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="117"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="37"/>
     </row>
     <row r="39" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="94"/>
-      <c r="J39" s="94"/>
-      <c r="K39" s="94"/>
-      <c r="L39" s="94"/>
-      <c r="M39" s="94"/>
-      <c r="N39" s="94"/>
-      <c r="O39" s="94"/>
-      <c r="P39" s="95"/>
+      <c r="A39" s="104"/>
+      <c r="B39" s="115"/>
+      <c r="C39" s="116"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="117"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="38"/>
+      <c r="P39" s="39"/>
     </row>
     <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="90" t="s">
+      <c r="A40" s="104"/>
+      <c r="B40" s="115"/>
+      <c r="C40" s="116"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="J40" s="90"/>
-      <c r="K40" s="90"/>
-      <c r="L40" s="90"/>
-      <c r="M40" s="90"/>
-      <c r="N40" s="90"/>
-      <c r="O40" s="90"/>
-      <c r="P40" s="91"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="30"/>
     </row>
     <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="65" t="s">
+      <c r="A41" s="104"/>
+      <c r="B41" s="115"/>
+      <c r="C41" s="116"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="117"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="117"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
-      <c r="N41" s="66"/>
-      <c r="O41" s="66"/>
-      <c r="P41" s="67"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+      <c r="N41" s="32"/>
+      <c r="O41" s="32"/>
+      <c r="P41" s="33"/>
     </row>
     <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="65" t="s">
+      <c r="A42" s="104"/>
+      <c r="B42" s="115"/>
+      <c r="C42" s="116"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="J42" s="66"/>
-      <c r="K42" s="66"/>
-      <c r="L42" s="66"/>
-      <c r="M42" s="66"/>
-      <c r="N42" s="66"/>
-      <c r="O42" s="66"/>
-      <c r="P42" s="67"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="33"/>
     </row>
     <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="65" t="s">
+      <c r="A43" s="104"/>
+      <c r="B43" s="115"/>
+      <c r="C43" s="116"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="118"/>
+      <c r="G43" s="117"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="J43" s="66"/>
-      <c r="K43" s="66"/>
-      <c r="L43" s="66"/>
-      <c r="M43" s="66"/>
-      <c r="N43" s="66"/>
-      <c r="O43" s="66"/>
-      <c r="P43" s="67"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="33"/>
     </row>
     <row r="44" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="65" t="s">
+      <c r="A44" s="104"/>
+      <c r="B44" s="115"/>
+      <c r="C44" s="116"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="117"/>
+      <c r="F44" s="118"/>
+      <c r="G44" s="117"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J44" s="66"/>
-      <c r="K44" s="66"/>
-      <c r="L44" s="66"/>
-      <c r="M44" s="66"/>
-      <c r="N44" s="66"/>
-      <c r="O44" s="66"/>
-      <c r="P44" s="67"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="33"/>
     </row>
     <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="65" t="s">
+      <c r="A45" s="104"/>
+      <c r="B45" s="115"/>
+      <c r="C45" s="116"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="117"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="J45" s="66"/>
-      <c r="K45" s="66"/>
-      <c r="L45" s="66"/>
-      <c r="M45" s="66"/>
-      <c r="N45" s="66"/>
-      <c r="O45" s="66"/>
-      <c r="P45" s="67"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="33"/>
     </row>
     <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="65" t="s">
+      <c r="A46" s="104"/>
+      <c r="B46" s="115"/>
+      <c r="C46" s="116"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="118"/>
+      <c r="G46" s="117"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="J46" s="66"/>
-      <c r="K46" s="66"/>
-      <c r="L46" s="66"/>
-      <c r="M46" s="66"/>
-      <c r="N46" s="66"/>
-      <c r="O46" s="66"/>
-      <c r="P46" s="67"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="33"/>
     </row>
     <row r="47" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="68" t="s">
+      <c r="A47" s="104"/>
+      <c r="B47" s="115"/>
+      <c r="C47" s="116"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="118"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="103"/>
+      <c r="I47" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="J47" s="69"/>
-      <c r="K47" s="69"/>
-      <c r="L47" s="69"/>
-      <c r="M47" s="69"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="69"/>
-      <c r="P47" s="70"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="80"/>
+      <c r="L47" s="80"/>
+      <c r="M47" s="80"/>
+      <c r="N47" s="80"/>
+      <c r="O47" s="80"/>
+      <c r="P47" s="81"/>
     </row>
     <row r="48" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="71" t="s">
+      <c r="A48" s="104"/>
+      <c r="B48" s="115"/>
+      <c r="C48" s="116"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="117"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="117"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="J48" s="72"/>
-      <c r="K48" s="72"/>
-      <c r="L48" s="72"/>
-      <c r="M48" s="72"/>
-      <c r="N48" s="72"/>
-      <c r="O48" s="72"/>
-      <c r="P48" s="73"/>
+      <c r="J48" s="83"/>
+      <c r="K48" s="83"/>
+      <c r="L48" s="83"/>
+      <c r="M48" s="83"/>
+      <c r="N48" s="83"/>
+      <c r="O48" s="83"/>
+      <c r="P48" s="84"/>
     </row>
     <row r="49" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="80" t="s">
+      <c r="A49" s="104"/>
+      <c r="B49" s="115"/>
+      <c r="C49" s="116"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="118"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="103"/>
+      <c r="I49" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="J49" s="81"/>
-      <c r="K49" s="83" t="s">
-        <v>28</v>
+      <c r="J49" s="92"/>
+      <c r="K49" s="94" t="s">
+        <v>27</v>
       </c>
-      <c r="L49" s="83"/>
-      <c r="M49" s="83"/>
-      <c r="N49" s="83"/>
-      <c r="O49" s="83"/>
-      <c r="P49" s="84"/>
+      <c r="L49" s="94"/>
+      <c r="M49" s="94"/>
+      <c r="N49" s="94"/>
+      <c r="O49" s="94"/>
+      <c r="P49" s="95"/>
     </row>
     <row r="50" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="80" t="s">
+      <c r="A50" s="104"/>
+      <c r="B50" s="115"/>
+      <c r="C50" s="116"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="117"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="J50" s="81"/>
-      <c r="K50" s="83" t="s">
+      <c r="J50" s="92"/>
+      <c r="K50" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="L50" s="83"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="83"/>
-      <c r="O50" s="83"/>
-      <c r="P50" s="84"/>
+      <c r="L50" s="94"/>
+      <c r="M50" s="94"/>
+      <c r="N50" s="94"/>
+      <c r="O50" s="94"/>
+      <c r="P50" s="95"/>
     </row>
     <row r="51" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="28"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="80" t="s">
+      <c r="A51" s="104"/>
+      <c r="B51" s="115"/>
+      <c r="C51" s="116"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="117"/>
+      <c r="H51" s="103"/>
+      <c r="I51" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="81"/>
-      <c r="K51" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="L51" s="83"/>
-      <c r="M51" s="83"/>
-      <c r="N51" s="83"/>
-      <c r="O51" s="83"/>
-      <c r="P51" s="84"/>
+      <c r="J51" s="92"/>
+      <c r="K51" s="94"/>
+      <c r="L51" s="94"/>
+      <c r="M51" s="94"/>
+      <c r="N51" s="94"/>
+      <c r="O51" s="94"/>
+      <c r="P51" s="95"/>
     </row>
     <row r="52" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="13"/>
@@ -2830,18 +2830,16 @@
       <c r="F52" s="12"/>
       <c r="G52" s="12"/>
       <c r="H52" s="14"/>
-      <c r="I52" s="80" t="s">
+      <c r="I52" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="J52" s="81"/>
-      <c r="K52" s="82">
-        <v>45252</v>
-      </c>
-      <c r="L52" s="83"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="83"/>
-      <c r="O52" s="83"/>
-      <c r="P52" s="84"/>
+      <c r="J52" s="92"/>
+      <c r="K52" s="93"/>
+      <c r="L52" s="94"/>
+      <c r="M52" s="94"/>
+      <c r="N52" s="94"/>
+      <c r="O52" s="94"/>
+      <c r="P52" s="95"/>
     </row>
     <row r="53" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="13"/>
@@ -2852,16 +2850,16 @@
       <c r="F53" s="12"/>
       <c r="G53" s="12"/>
       <c r="H53" s="14"/>
-      <c r="I53" s="85" t="s">
+      <c r="I53" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="J53" s="86"/>
-      <c r="K53" s="86"/>
-      <c r="L53" s="86"/>
-      <c r="M53" s="86"/>
-      <c r="N53" s="86"/>
-      <c r="O53" s="86"/>
-      <c r="P53" s="87"/>
+      <c r="J53" s="97"/>
+      <c r="K53" s="97"/>
+      <c r="L53" s="97"/>
+      <c r="M53" s="97"/>
+      <c r="N53" s="97"/>
+      <c r="O53" s="97"/>
+      <c r="P53" s="98"/>
     </row>
     <row r="54" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="13"/>
@@ -2872,16 +2870,16 @@
       <c r="F54" s="12"/>
       <c r="G54" s="12"/>
       <c r="H54" s="14"/>
-      <c r="I54" s="74" t="s">
+      <c r="I54" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="J54" s="75"/>
-      <c r="K54" s="75"/>
-      <c r="L54" s="75"/>
-      <c r="M54" s="75"/>
-      <c r="N54" s="75"/>
-      <c r="O54" s="75"/>
-      <c r="P54" s="76"/>
+      <c r="J54" s="86"/>
+      <c r="K54" s="86"/>
+      <c r="L54" s="86"/>
+      <c r="M54" s="86"/>
+      <c r="N54" s="86"/>
+      <c r="O54" s="86"/>
+      <c r="P54" s="87"/>
     </row>
     <row r="55" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="13"/>
@@ -2892,14 +2890,14 @@
       <c r="F55" s="12"/>
       <c r="G55" s="12"/>
       <c r="H55" s="14"/>
-      <c r="I55" s="74"/>
-      <c r="J55" s="75"/>
-      <c r="K55" s="75"/>
-      <c r="L55" s="75"/>
-      <c r="M55" s="75"/>
-      <c r="N55" s="75"/>
-      <c r="O55" s="75"/>
-      <c r="P55" s="76"/>
+      <c r="I55" s="85"/>
+      <c r="J55" s="86"/>
+      <c r="K55" s="86"/>
+      <c r="L55" s="86"/>
+      <c r="M55" s="86"/>
+      <c r="N55" s="86"/>
+      <c r="O55" s="86"/>
+      <c r="P55" s="87"/>
     </row>
     <row r="56" spans="1:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="13"/>
@@ -2910,14 +2908,14 @@
       <c r="F56" s="12"/>
       <c r="G56" s="12"/>
       <c r="H56" s="14"/>
-      <c r="I56" s="74"/>
-      <c r="J56" s="75"/>
-      <c r="K56" s="75"/>
-      <c r="L56" s="75"/>
-      <c r="M56" s="75"/>
-      <c r="N56" s="75"/>
-      <c r="O56" s="75"/>
-      <c r="P56" s="76"/>
+      <c r="I56" s="85"/>
+      <c r="J56" s="86"/>
+      <c r="K56" s="86"/>
+      <c r="L56" s="86"/>
+      <c r="M56" s="86"/>
+      <c r="N56" s="86"/>
+      <c r="O56" s="86"/>
+      <c r="P56" s="87"/>
     </row>
     <row r="57" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13"/>
@@ -2928,14 +2926,14 @@
       <c r="F57" s="12"/>
       <c r="G57" s="12"/>
       <c r="H57" s="14"/>
-      <c r="I57" s="77"/>
-      <c r="J57" s="78"/>
-      <c r="K57" s="78"/>
-      <c r="L57" s="78"/>
-      <c r="M57" s="78"/>
-      <c r="N57" s="78"/>
-      <c r="O57" s="78"/>
-      <c r="P57" s="79"/>
+      <c r="I57" s="88"/>
+      <c r="J57" s="89"/>
+      <c r="K57" s="89"/>
+      <c r="L57" s="89"/>
+      <c r="M57" s="89"/>
+      <c r="N57" s="89"/>
+      <c r="O57" s="89"/>
+      <c r="P57" s="90"/>
     </row>
     <row r="58" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="15"/>
@@ -2946,19 +2944,153 @@
       <c r="F58" s="18"/>
       <c r="G58" s="18"/>
       <c r="H58" s="19"/>
-      <c r="I58" s="63" t="s">
+      <c r="I58" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="J58" s="63"/>
-      <c r="K58" s="63"/>
-      <c r="L58" s="63"/>
-      <c r="M58" s="63"/>
-      <c r="N58" s="63"/>
-      <c r="O58" s="63"/>
-      <c r="P58" s="64"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="77"/>
+      <c r="L58" s="77"/>
+      <c r="M58" s="77"/>
+      <c r="N58" s="77"/>
+      <c r="O58" s="77"/>
+      <c r="P58" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="158">
+    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="H49:H51"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="H40:H42"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="H43:H45"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="H34:H36"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="H37:H39"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="I58:P58"/>
+    <mergeCell ref="I43:P43"/>
+    <mergeCell ref="I44:P44"/>
+    <mergeCell ref="I45:P45"/>
+    <mergeCell ref="I46:P46"/>
+    <mergeCell ref="I47:P47"/>
+    <mergeCell ref="I48:P48"/>
+    <mergeCell ref="I54:P57"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="K52:P52"/>
+    <mergeCell ref="K49:P49"/>
+    <mergeCell ref="K50:P50"/>
+    <mergeCell ref="K51:P51"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:P53"/>
     <mergeCell ref="U16:Y16"/>
     <mergeCell ref="U17:Y17"/>
     <mergeCell ref="I40:P40"/>
@@ -2983,140 +3115,6 @@
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="C4:C6"/>
-    <mergeCell ref="I58:P58"/>
-    <mergeCell ref="I43:P43"/>
-    <mergeCell ref="I44:P44"/>
-    <mergeCell ref="I45:P45"/>
-    <mergeCell ref="I46:P46"/>
-    <mergeCell ref="I47:P47"/>
-    <mergeCell ref="I48:P48"/>
-    <mergeCell ref="I54:P57"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K52:P52"/>
-    <mergeCell ref="K49:P49"/>
-    <mergeCell ref="K50:P50"/>
-    <mergeCell ref="K51:P51"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:P53"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="H16:H18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="H34:H36"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="H37:H39"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="H40:H42"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="G43:G45"/>
-    <mergeCell ref="H43:H45"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="H46:H48"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="E49:E51"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="H49:H51"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="A46:A48"/>
   </mergeCells>
   <conditionalFormatting sqref="E4 M4:M12 E7:E58">
     <cfRule type="notContainsBlanks" dxfId="1" priority="2" stopIfTrue="1">
